--- a/education_forms/018_free_math_tutoring--education_forms.xlsx
+++ b/education_forms/018_free_math_tutoring--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>output_file_format</t>
+          <t>output_file_format_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Output File Format</t>
+          <t>Output File Format 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>output_file_path</t>
+          <t>output_file_path_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Output File Path</t>
+          <t>Output File Path 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Form Title</t>
+          <t>Form Title 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1109,7 +1109,7 @@
   <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>76765</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>76765</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1678,7 +1678,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>output_file_format_choices</t>
+          <t>output_file_format_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>output_file_format_choices</t>
+          <t>output_file_format_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>output_file_format_choices</t>
+          <t>output_file_format_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1729,58 +1729,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>form_id_choices</t>
+          <t>form_id_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>form_id_choices</t>
+          <t>form_id_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>76765</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>76765</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>form_id_choices</t>
+          <t>form_id_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1797,7 +1797,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1814,7 +1814,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
